--- a/public/cigar-import-template.xlsx
+++ b/public/cigar-import-template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原盒" sheetId="1" r:id="R0ce34b0d06d64c78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="散支" sheetId="2" r:id="R6ad2fe7f456d47ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原盒" sheetId="1" r:id="Rd81bc50269e24195"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="散支" sheetId="2" r:id="R72a15b8eaa0a4ec2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,10 +14,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="¥#,##0.00"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
+    <x:numFmt numFmtId="203" formatCode="yyyy-mm-dd hh:mm"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -36,7 +37,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -53,8 +54,13 @@
         <x:fgColor rgb="FFF2F2FA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6574C3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -104,11 +110,25 @@
         <x:color rgb="FFDEDDEB"/>
       </x:left>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF5362AD"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF5362AD"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF5362AD"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF5362AD"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -154,6 +174,23 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -367,6 +404,7 @@
     <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -397,6 +435,9 @@
       <x:c r="I1" s="11" t="str">
         <x:v>柜号</x:v>
       </x:c>
+      <x:c r="J1" s="27" t="str">
+        <x:v>入库时间</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="17" t="str">
@@ -425,6 +466,9 @@
       </x:c>
       <x:c r="I2" s="19" t="str">
         <x:v>M</x:v>
+      </x:c>
+      <x:c r="J2" s="31" t="n">
+        <x:v>45306.083333333336</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -442,6 +486,7 @@
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -463,6 +508,9 @@
       <x:c r="F1" s="11" t="str">
         <x:v>柜号</x:v>
       </x:c>
+      <x:c r="G1" s="27" t="str">
+        <x:v>入库时间</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="17" t="str">
@@ -482,6 +530,9 @@
       </x:c>
       <x:c r="F2" s="19" t="str">
         <x:v>M</x:v>
+      </x:c>
+      <x:c r="G2" s="31" t="n">
+        <x:v>45306.083333333336</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
